--- a/dashboard_data/latest_sourcing_rank.xlsx
+++ b/dashboard_data/latest_sourcing_rank.xlsx
@@ -63,7 +63,7 @@
     <t>주의</t>
   </si>
   <si>
-    <t>2026-06-21 15:58:46</t>
+    <t>2026-06-21 16:11:00</t>
   </si>
   <si>
     <t>점수는 소싱 후보 선별용입니다. 식품/화장품/KC/상표권/정품 증빙은 등록 전 별도 확인하세요.</t>
@@ -1343,16 +1343,16 @@
         <v>0</v>
       </c>
       <c r="M3" s="2">
-        <v>154855</v>
+        <v>154860</v>
       </c>
       <c r="N3">
-        <v>23413</v>
+        <v>23414</v>
       </c>
       <c r="O3">
-        <v>0.1511930515643667</v>
+        <v>0.1511946274053984</v>
       </c>
       <c r="P3">
-        <v>3.90082082252371</v>
+        <v>3.900654928978481</v>
       </c>
       <c r="Q3">
         <v>50747</v>
@@ -1491,16 +1491,16 @@
         <v>0</v>
       </c>
       <c r="M5" s="2">
-        <v>43953</v>
+        <v>43956</v>
       </c>
       <c r="N5">
-        <v>12689</v>
+        <v>12690</v>
       </c>
       <c r="O5">
-        <v>0.2886947421108912</v>
+        <v>0.2886977886977887</v>
       </c>
       <c r="P5">
-        <v>5.840175150519978</v>
+        <v>5.839718530101642</v>
       </c>
       <c r="Q5">
         <v>89641</v>
@@ -1639,13 +1639,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>29649</v>
+        <v>29650</v>
       </c>
       <c r="N7">
         <v>10933</v>
       </c>
       <c r="O7">
-        <v>0.3687476812034133</v>
+        <v>0.3687352445193929</v>
       </c>
       <c r="P7">
         <v>4.501042327562766</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="2">
-        <v>94336</v>
+        <v>94337</v>
       </c>
       <c r="N8">
         <v>20945</v>
       </c>
       <c r="O8">
-        <v>0.22202552578019</v>
+        <v>0.2220231722441884</v>
       </c>
       <c r="P8">
         <v>3.524827750059397</v>
@@ -1858,16 +1858,16 @@
         <v>0</v>
       </c>
       <c r="M10" s="2">
-        <v>66850</v>
+        <v>66853</v>
       </c>
       <c r="N10">
-        <v>15954</v>
+        <v>15955</v>
       </c>
       <c r="O10">
-        <v>0.2386537023186238</v>
+        <v>0.2386579510268799</v>
       </c>
       <c r="P10">
-        <v>1.854366513018562</v>
+        <v>1.854251012145749</v>
       </c>
       <c r="Q10">
         <v>61648</v>
@@ -1932,16 +1932,16 @@
         <v>0</v>
       </c>
       <c r="M11" s="2">
-        <v>72885</v>
+        <v>72889</v>
       </c>
       <c r="N11">
-        <v>45257</v>
+        <v>45261</v>
       </c>
       <c r="O11">
-        <v>0.6209370926802497</v>
+        <v>0.6209578948812579</v>
       </c>
       <c r="P11">
-        <v>0.8666798950547876</v>
+        <v>0.8666034699411389</v>
       </c>
       <c r="Q11">
         <v>106848</v>
@@ -2080,13 +2080,13 @@
         <v>0</v>
       </c>
       <c r="M13" s="2">
-        <v>101730</v>
+        <v>101734</v>
       </c>
       <c r="N13">
         <v>20523</v>
       </c>
       <c r="O13">
-        <v>0.2017398997345916</v>
+        <v>0.2017319676804215</v>
       </c>
       <c r="P13">
         <v>1.111380497502788</v>
@@ -2151,13 +2151,13 @@
         <v>0</v>
       </c>
       <c r="M14" s="2">
-        <v>23856</v>
+        <v>23855</v>
       </c>
       <c r="N14">
         <v>10817</v>
       </c>
       <c r="O14">
-        <v>0.4534289067739772</v>
+        <v>0.4534479144833368</v>
       </c>
       <c r="P14">
         <v>2.261610332508931</v>
@@ -2299,13 +2299,13 @@
         <v>0</v>
       </c>
       <c r="M16" s="2">
-        <v>38696</v>
+        <v>38697</v>
       </c>
       <c r="N16">
         <v>4180</v>
       </c>
       <c r="O16">
-        <v>0.1080215009303287</v>
+        <v>0.1080187094606817</v>
       </c>
       <c r="P16">
         <v>2.186915887850467</v>
@@ -2373,16 +2373,16 @@
         <v>0</v>
       </c>
       <c r="M17" s="2">
-        <v>379697</v>
+        <v>379708</v>
       </c>
       <c r="N17">
-        <v>52873</v>
+        <v>52875</v>
       </c>
       <c r="O17">
-        <v>0.1392505076416195</v>
+        <v>0.1392517408113603</v>
       </c>
       <c r="P17">
-        <v>0.7294281992713268</v>
+        <v>0.7294006606890042</v>
       </c>
       <c r="Q17">
         <v>46595</v>
@@ -2521,16 +2521,16 @@
         <v>0</v>
       </c>
       <c r="M19" s="2">
-        <v>149907</v>
+        <v>149776</v>
       </c>
       <c r="N19">
-        <v>68691</v>
+        <v>68686</v>
       </c>
       <c r="O19">
-        <v>0.4582240989413436</v>
+        <v>0.4585914966349749</v>
       </c>
       <c r="P19">
-        <v>0.7854225116657703</v>
+        <v>0.7854796034076702</v>
       </c>
       <c r="Q19">
         <v>101539</v>
@@ -2595,13 +2595,13 @@
         <v>0</v>
       </c>
       <c r="M20" s="2">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="N20">
         <v>1414</v>
       </c>
       <c r="O20">
-        <v>0.7372262773722628</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="P20">
         <v>5.82562747688243</v>
@@ -2669,16 +2669,16 @@
         <v>0</v>
       </c>
       <c r="M21" s="2">
-        <v>89494</v>
+        <v>89495</v>
       </c>
       <c r="N21">
-        <v>11075</v>
+        <v>11076</v>
       </c>
       <c r="O21">
-        <v>0.1237513129371801</v>
+        <v>0.123761103972289</v>
       </c>
       <c r="P21">
-        <v>2.730201342281879</v>
+        <v>2.729957050823193</v>
       </c>
       <c r="Q21">
         <v>15396</v>
@@ -2817,16 +2817,16 @@
         <v>0</v>
       </c>
       <c r="M23" s="2">
-        <v>422657</v>
+        <v>422659</v>
       </c>
       <c r="N23">
-        <v>280393</v>
+        <v>280397</v>
       </c>
       <c r="O23">
-        <v>0.663405551073329</v>
+        <v>0.6634118757674626</v>
       </c>
       <c r="P23">
-        <v>0.2917719871797157</v>
+        <v>0.2917678263938652</v>
       </c>
       <c r="Q23">
         <v>156599</v>
@@ -2891,16 +2891,16 @@
         <v>0</v>
       </c>
       <c r="M24" s="2">
-        <v>1908861</v>
+        <v>1908183</v>
       </c>
       <c r="N24">
-        <v>705879</v>
+        <v>705901</v>
       </c>
       <c r="O24">
-        <v>0.3697906762200077</v>
+        <v>0.3699335965156382</v>
       </c>
       <c r="P24">
-        <v>0.2215363346501808</v>
+        <v>0.2215294312614288</v>
       </c>
       <c r="Q24">
         <v>91990</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="M25" s="2">
-        <v>346536</v>
+        <v>346537</v>
       </c>
       <c r="N25">
-        <v>77853</v>
+        <v>77854</v>
       </c>
       <c r="O25">
-        <v>0.2246606413186509</v>
+        <v>0.2246628787113641</v>
       </c>
       <c r="P25">
-        <v>0.477980321475761</v>
+        <v>0.4779741899068681</v>
       </c>
       <c r="Q25">
         <v>30810</v>
@@ -3039,16 +3039,16 @@
         <v>0</v>
       </c>
       <c r="M26" s="2">
-        <v>93986</v>
+        <v>93989</v>
       </c>
       <c r="N26">
-        <v>17044</v>
+        <v>17045</v>
       </c>
       <c r="O26">
-        <v>0.1813461579384164</v>
+        <v>0.1813510091606464</v>
       </c>
       <c r="P26">
-        <v>0.919272048530098</v>
+        <v>0.9192184310294547</v>
       </c>
       <c r="Q26">
         <v>40699</v>
@@ -3113,16 +3113,16 @@
         <v>0</v>
       </c>
       <c r="M27" s="2">
-        <v>1376945</v>
+        <v>1376959</v>
       </c>
       <c r="N27">
-        <v>517405</v>
+        <v>517411</v>
       </c>
       <c r="O27">
-        <v>0.3757630115945081</v>
+        <v>0.3757635485152426</v>
       </c>
       <c r="P27">
-        <v>0.1991671578052386</v>
+        <v>0.1991648486698833</v>
       </c>
       <c r="Q27">
         <v>50682</v>
@@ -3187,13 +3187,13 @@
         <v>0</v>
       </c>
       <c r="M28" s="2">
-        <v>138453</v>
+        <v>138456</v>
       </c>
       <c r="N28">
         <v>19476</v>
       </c>
       <c r="O28">
-        <v>0.140668674568265</v>
+        <v>0.140665626625065</v>
       </c>
       <c r="P28">
         <v>0.3902738046587658</v>
@@ -3258,16 +3258,16 @@
         <v>0</v>
       </c>
       <c r="M29" s="2">
-        <v>268622</v>
+        <v>268638</v>
       </c>
       <c r="N29">
-        <v>34451</v>
+        <v>34453</v>
       </c>
       <c r="O29">
-        <v>0.1282508506376991</v>
+        <v>0.1282506570179945</v>
       </c>
       <c r="P29">
-        <v>0.4824751816155828</v>
+        <v>0.4824472549416838</v>
       </c>
       <c r="Q29">
         <v>35560</v>
@@ -3757,16 +3757,16 @@
         <v>0</v>
       </c>
       <c r="M3" s="2">
-        <v>154855</v>
+        <v>154860</v>
       </c>
       <c r="N3">
-        <v>23413</v>
+        <v>23414</v>
       </c>
       <c r="O3">
-        <v>0.1511930515643667</v>
+        <v>0.1511946274053984</v>
       </c>
       <c r="P3">
-        <v>3.90082082252371</v>
+        <v>3.900654928978481</v>
       </c>
       <c r="Q3">
         <v>50747</v>
@@ -3905,16 +3905,16 @@
         <v>0</v>
       </c>
       <c r="M5" s="2">
-        <v>43953</v>
+        <v>43956</v>
       </c>
       <c r="N5">
-        <v>12689</v>
+        <v>12690</v>
       </c>
       <c r="O5">
-        <v>0.2886947421108912</v>
+        <v>0.2886977886977887</v>
       </c>
       <c r="P5">
-        <v>5.840175150519978</v>
+        <v>5.839718530101642</v>
       </c>
       <c r="Q5">
         <v>89641</v>
@@ -4053,13 +4053,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>29649</v>
+        <v>29650</v>
       </c>
       <c r="N7">
         <v>10933</v>
       </c>
       <c r="O7">
-        <v>0.3687476812034133</v>
+        <v>0.3687352445193929</v>
       </c>
       <c r="P7">
         <v>4.501042327562766</v>
@@ -4127,13 +4127,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="2">
-        <v>94336</v>
+        <v>94337</v>
       </c>
       <c r="N8">
         <v>20945</v>
       </c>
       <c r="O8">
-        <v>0.22202552578019</v>
+        <v>0.2220231722441884</v>
       </c>
       <c r="P8">
         <v>3.524827750059397</v>
@@ -4272,16 +4272,16 @@
         <v>0</v>
       </c>
       <c r="M10" s="2">
-        <v>66850</v>
+        <v>66853</v>
       </c>
       <c r="N10">
-        <v>15954</v>
+        <v>15955</v>
       </c>
       <c r="O10">
-        <v>0.2386537023186238</v>
+        <v>0.2386579510268799</v>
       </c>
       <c r="P10">
-        <v>1.854366513018562</v>
+        <v>1.854251012145749</v>
       </c>
       <c r="Q10">
         <v>61648</v>
@@ -4346,16 +4346,16 @@
         <v>0</v>
       </c>
       <c r="M11" s="2">
-        <v>72885</v>
+        <v>72889</v>
       </c>
       <c r="N11">
-        <v>45257</v>
+        <v>45261</v>
       </c>
       <c r="O11">
-        <v>0.6209370926802497</v>
+        <v>0.6209578948812579</v>
       </c>
       <c r="P11">
-        <v>0.8666798950547876</v>
+        <v>0.8666034699411389</v>
       </c>
       <c r="Q11">
         <v>106848</v>
@@ -4494,13 +4494,13 @@
         <v>0</v>
       </c>
       <c r="M13" s="2">
-        <v>101730</v>
+        <v>101734</v>
       </c>
       <c r="N13">
         <v>20523</v>
       </c>
       <c r="O13">
-        <v>0.2017398997345916</v>
+        <v>0.2017319676804215</v>
       </c>
       <c r="P13">
         <v>1.111380497502788</v>
@@ -4565,13 +4565,13 @@
         <v>0</v>
       </c>
       <c r="M14" s="2">
-        <v>23856</v>
+        <v>23855</v>
       </c>
       <c r="N14">
         <v>10817</v>
       </c>
       <c r="O14">
-        <v>0.4534289067739772</v>
+        <v>0.4534479144833368</v>
       </c>
       <c r="P14">
         <v>2.261610332508931</v>
@@ -4713,13 +4713,13 @@
         <v>0</v>
       </c>
       <c r="M16" s="2">
-        <v>38696</v>
+        <v>38697</v>
       </c>
       <c r="N16">
         <v>4180</v>
       </c>
       <c r="O16">
-        <v>0.1080215009303287</v>
+        <v>0.1080187094606817</v>
       </c>
       <c r="P16">
         <v>2.186915887850467</v>
@@ -4787,16 +4787,16 @@
         <v>0</v>
       </c>
       <c r="M17" s="2">
-        <v>379697</v>
+        <v>379708</v>
       </c>
       <c r="N17">
-        <v>52873</v>
+        <v>52875</v>
       </c>
       <c r="O17">
-        <v>0.1392505076416195</v>
+        <v>0.1392517408113603</v>
       </c>
       <c r="P17">
-        <v>0.7294281992713268</v>
+        <v>0.7294006606890042</v>
       </c>
       <c r="Q17">
         <v>46595</v>
@@ -4935,16 +4935,16 @@
         <v>0</v>
       </c>
       <c r="M19" s="2">
-        <v>149907</v>
+        <v>149776</v>
       </c>
       <c r="N19">
-        <v>68691</v>
+        <v>68686</v>
       </c>
       <c r="O19">
-        <v>0.4582240989413436</v>
+        <v>0.4585914966349749</v>
       </c>
       <c r="P19">
-        <v>0.7854225116657703</v>
+        <v>0.7854796034076702</v>
       </c>
       <c r="Q19">
         <v>101539</v>
@@ -5009,13 +5009,13 @@
         <v>0</v>
       </c>
       <c r="M20" s="2">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="N20">
         <v>1414</v>
       </c>
       <c r="O20">
-        <v>0.7372262773722628</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="P20">
         <v>5.82562747688243</v>
@@ -5083,16 +5083,16 @@
         <v>0</v>
       </c>
       <c r="M21" s="2">
-        <v>89494</v>
+        <v>89495</v>
       </c>
       <c r="N21">
-        <v>11075</v>
+        <v>11076</v>
       </c>
       <c r="O21">
-        <v>0.1237513129371801</v>
+        <v>0.123761103972289</v>
       </c>
       <c r="P21">
-        <v>2.730201342281879</v>
+        <v>2.729957050823193</v>
       </c>
       <c r="Q21">
         <v>15396</v>
@@ -5231,16 +5231,16 @@
         <v>0</v>
       </c>
       <c r="M23" s="2">
-        <v>422657</v>
+        <v>422659</v>
       </c>
       <c r="N23">
-        <v>280393</v>
+        <v>280397</v>
       </c>
       <c r="O23">
-        <v>0.663405551073329</v>
+        <v>0.6634118757674626</v>
       </c>
       <c r="P23">
-        <v>0.2917719871797157</v>
+        <v>0.2917678263938652</v>
       </c>
       <c r="Q23">
         <v>156599</v>
@@ -5305,16 +5305,16 @@
         <v>0</v>
       </c>
       <c r="M24" s="2">
-        <v>1908861</v>
+        <v>1908183</v>
       </c>
       <c r="N24">
-        <v>705879</v>
+        <v>705901</v>
       </c>
       <c r="O24">
-        <v>0.3697906762200077</v>
+        <v>0.3699335965156382</v>
       </c>
       <c r="P24">
-        <v>0.2215363346501808</v>
+        <v>0.2215294312614288</v>
       </c>
       <c r="Q24">
         <v>91990</v>
@@ -5379,16 +5379,16 @@
         <v>0</v>
       </c>
       <c r="M25" s="2">
-        <v>346536</v>
+        <v>346537</v>
       </c>
       <c r="N25">
-        <v>77853</v>
+        <v>77854</v>
       </c>
       <c r="O25">
-        <v>0.2246606413186509</v>
+        <v>0.2246628787113641</v>
       </c>
       <c r="P25">
-        <v>0.477980321475761</v>
+        <v>0.4779741899068681</v>
       </c>
       <c r="Q25">
         <v>30810</v>
@@ -5453,16 +5453,16 @@
         <v>0</v>
       </c>
       <c r="M26" s="2">
-        <v>93986</v>
+        <v>93989</v>
       </c>
       <c r="N26">
-        <v>17044</v>
+        <v>17045</v>
       </c>
       <c r="O26">
-        <v>0.1813461579384164</v>
+        <v>0.1813510091606464</v>
       </c>
       <c r="P26">
-        <v>0.919272048530098</v>
+        <v>0.9192184310294547</v>
       </c>
       <c r="Q26">
         <v>40699</v>
@@ -5527,16 +5527,16 @@
         <v>0</v>
       </c>
       <c r="M27" s="2">
-        <v>1376945</v>
+        <v>1376959</v>
       </c>
       <c r="N27">
-        <v>517405</v>
+        <v>517411</v>
       </c>
       <c r="O27">
-        <v>0.3757630115945081</v>
+        <v>0.3757635485152426</v>
       </c>
       <c r="P27">
-        <v>0.1991671578052386</v>
+        <v>0.1991648486698833</v>
       </c>
       <c r="Q27">
         <v>50682</v>
@@ -5601,13 +5601,13 @@
         <v>0</v>
       </c>
       <c r="M28" s="2">
-        <v>138453</v>
+        <v>138456</v>
       </c>
       <c r="N28">
         <v>19476</v>
       </c>
       <c r="O28">
-        <v>0.140668674568265</v>
+        <v>0.140665626625065</v>
       </c>
       <c r="P28">
         <v>0.3902738046587658</v>
@@ -5672,16 +5672,16 @@
         <v>0</v>
       </c>
       <c r="M29" s="2">
-        <v>268622</v>
+        <v>268638</v>
       </c>
       <c r="N29">
-        <v>34451</v>
+        <v>34453</v>
       </c>
       <c r="O29">
-        <v>0.1282508506376991</v>
+        <v>0.1282506570179945</v>
       </c>
       <c r="P29">
-        <v>0.4824751816155828</v>
+        <v>0.4824472549416838</v>
       </c>
       <c r="Q29">
         <v>35560</v>
@@ -6063,16 +6063,16 @@
         <v>0</v>
       </c>
       <c r="M3" s="2">
-        <v>154855</v>
+        <v>154860</v>
       </c>
       <c r="N3">
-        <v>23413</v>
+        <v>23414</v>
       </c>
       <c r="O3">
-        <v>0.1511930515643667</v>
+        <v>0.1511946274053984</v>
       </c>
       <c r="P3">
-        <v>3.90082082252371</v>
+        <v>3.900654928978481</v>
       </c>
       <c r="Q3">
         <v>50747</v>
@@ -6211,16 +6211,16 @@
         <v>0</v>
       </c>
       <c r="M5" s="2">
-        <v>43953</v>
+        <v>43956</v>
       </c>
       <c r="N5">
-        <v>12689</v>
+        <v>12690</v>
       </c>
       <c r="O5">
-        <v>0.2886947421108912</v>
+        <v>0.2886977886977887</v>
       </c>
       <c r="P5">
-        <v>5.840175150519978</v>
+        <v>5.839718530101642</v>
       </c>
       <c r="Q5">
         <v>89641</v>
@@ -6359,13 +6359,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>29649</v>
+        <v>29650</v>
       </c>
       <c r="N7">
         <v>10933</v>
       </c>
       <c r="O7">
-        <v>0.3687476812034133</v>
+        <v>0.3687352445193929</v>
       </c>
       <c r="P7">
         <v>4.501042327562766</v>
@@ -6433,13 +6433,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="2">
-        <v>94336</v>
+        <v>94337</v>
       </c>
       <c r="N8">
         <v>20945</v>
       </c>
       <c r="O8">
-        <v>0.22202552578019</v>
+        <v>0.2220231722441884</v>
       </c>
       <c r="P8">
         <v>3.524827750059397</v>
@@ -6578,16 +6578,16 @@
         <v>0</v>
       </c>
       <c r="M10" s="2">
-        <v>66850</v>
+        <v>66853</v>
       </c>
       <c r="N10">
-        <v>15954</v>
+        <v>15955</v>
       </c>
       <c r="O10">
-        <v>0.2386537023186238</v>
+        <v>0.2386579510268799</v>
       </c>
       <c r="P10">
-        <v>1.854366513018562</v>
+        <v>1.854251012145749</v>
       </c>
       <c r="Q10">
         <v>61648</v>
@@ -6652,16 +6652,16 @@
         <v>0</v>
       </c>
       <c r="M11" s="2">
-        <v>72885</v>
+        <v>72889</v>
       </c>
       <c r="N11">
-        <v>45257</v>
+        <v>45261</v>
       </c>
       <c r="O11">
-        <v>0.6209370926802497</v>
+        <v>0.6209578948812579</v>
       </c>
       <c r="P11">
-        <v>0.8666798950547876</v>
+        <v>0.8666034699411389</v>
       </c>
       <c r="Q11">
         <v>106848</v>
@@ -6800,13 +6800,13 @@
         <v>0</v>
       </c>
       <c r="M13" s="2">
-        <v>101730</v>
+        <v>101734</v>
       </c>
       <c r="N13">
         <v>20523</v>
       </c>
       <c r="O13">
-        <v>0.2017398997345916</v>
+        <v>0.2017319676804215</v>
       </c>
       <c r="P13">
         <v>1.111380497502788</v>
@@ -6871,13 +6871,13 @@
         <v>0</v>
       </c>
       <c r="M14" s="2">
-        <v>23856</v>
+        <v>23855</v>
       </c>
       <c r="N14">
         <v>10817</v>
       </c>
       <c r="O14">
-        <v>0.4534289067739772</v>
+        <v>0.4534479144833368</v>
       </c>
       <c r="P14">
         <v>2.261610332508931</v>
@@ -7019,13 +7019,13 @@
         <v>0</v>
       </c>
       <c r="M16" s="2">
-        <v>38696</v>
+        <v>38697</v>
       </c>
       <c r="N16">
         <v>4180</v>
       </c>
       <c r="O16">
-        <v>0.1080215009303287</v>
+        <v>0.1080187094606817</v>
       </c>
       <c r="P16">
         <v>2.186915887850467</v>
@@ -7093,16 +7093,16 @@
         <v>0</v>
       </c>
       <c r="M17" s="2">
-        <v>379697</v>
+        <v>379708</v>
       </c>
       <c r="N17">
-        <v>52873</v>
+        <v>52875</v>
       </c>
       <c r="O17">
-        <v>0.1392505076416195</v>
+        <v>0.1392517408113603</v>
       </c>
       <c r="P17">
-        <v>0.7294281992713268</v>
+        <v>0.7294006606890042</v>
       </c>
       <c r="Q17">
         <v>46595</v>
@@ -7241,16 +7241,16 @@
         <v>0</v>
       </c>
       <c r="M19" s="2">
-        <v>149907</v>
+        <v>149776</v>
       </c>
       <c r="N19">
-        <v>68691</v>
+        <v>68686</v>
       </c>
       <c r="O19">
-        <v>0.4582240989413436</v>
+        <v>0.4585914966349749</v>
       </c>
       <c r="P19">
-        <v>0.7854225116657703</v>
+        <v>0.7854796034076702</v>
       </c>
       <c r="Q19">
         <v>101539</v>
@@ -7315,13 +7315,13 @@
         <v>0</v>
       </c>
       <c r="M20" s="2">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="N20">
         <v>1414</v>
       </c>
       <c r="O20">
-        <v>0.7372262773722628</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="P20">
         <v>5.82562747688243</v>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="M21" s="2">
-        <v>89494</v>
+        <v>89495</v>
       </c>
       <c r="N21">
-        <v>11075</v>
+        <v>11076</v>
       </c>
       <c r="O21">
-        <v>0.1237513129371801</v>
+        <v>0.123761103972289</v>
       </c>
       <c r="P21">
-        <v>2.730201342281879</v>
+        <v>2.729957050823193</v>
       </c>
       <c r="Q21">
         <v>15396</v>
@@ -7537,16 +7537,16 @@
         <v>0</v>
       </c>
       <c r="M23" s="2">
-        <v>422657</v>
+        <v>422659</v>
       </c>
       <c r="N23">
-        <v>280393</v>
+        <v>280397</v>
       </c>
       <c r="O23">
-        <v>0.663405551073329</v>
+        <v>0.6634118757674626</v>
       </c>
       <c r="P23">
-        <v>0.2917719871797157</v>
+        <v>0.2917678263938652</v>
       </c>
       <c r="Q23">
         <v>156599</v>
@@ -7611,16 +7611,16 @@
         <v>0</v>
       </c>
       <c r="M24" s="2">
-        <v>1908861</v>
+        <v>1908183</v>
       </c>
       <c r="N24">
-        <v>705879</v>
+        <v>705901</v>
       </c>
       <c r="O24">
-        <v>0.3697906762200077</v>
+        <v>0.3699335965156382</v>
       </c>
       <c r="P24">
-        <v>0.2215363346501808</v>
+        <v>0.2215294312614288</v>
       </c>
       <c r="Q24">
         <v>91990</v>
@@ -7685,16 +7685,16 @@
         <v>0</v>
       </c>
       <c r="M25" s="2">
-        <v>346536</v>
+        <v>346537</v>
       </c>
       <c r="N25">
-        <v>77853</v>
+        <v>77854</v>
       </c>
       <c r="O25">
-        <v>0.2246606413186509</v>
+        <v>0.2246628787113641</v>
       </c>
       <c r="P25">
-        <v>0.477980321475761</v>
+        <v>0.4779741899068681</v>
       </c>
       <c r="Q25">
         <v>30810</v>
@@ -7759,16 +7759,16 @@
         <v>0</v>
       </c>
       <c r="M26" s="2">
-        <v>93986</v>
+        <v>93989</v>
       </c>
       <c r="N26">
-        <v>17044</v>
+        <v>17045</v>
       </c>
       <c r="O26">
-        <v>0.1813461579384164</v>
+        <v>0.1813510091606464</v>
       </c>
       <c r="P26">
-        <v>0.919272048530098</v>
+        <v>0.9192184310294547</v>
       </c>
       <c r="Q26">
         <v>40699</v>
@@ -7833,16 +7833,16 @@
         <v>0</v>
       </c>
       <c r="M27" s="2">
-        <v>1376945</v>
+        <v>1376959</v>
       </c>
       <c r="N27">
-        <v>517405</v>
+        <v>517411</v>
       </c>
       <c r="O27">
-        <v>0.3757630115945081</v>
+        <v>0.3757635485152426</v>
       </c>
       <c r="P27">
-        <v>0.1991671578052386</v>
+        <v>0.1991648486698833</v>
       </c>
       <c r="Q27">
         <v>50682</v>
@@ -7907,13 +7907,13 @@
         <v>0</v>
       </c>
       <c r="M28" s="2">
-        <v>138453</v>
+        <v>138456</v>
       </c>
       <c r="N28">
         <v>19476</v>
       </c>
       <c r="O28">
-        <v>0.140668674568265</v>
+        <v>0.140665626625065</v>
       </c>
       <c r="P28">
         <v>0.3902738046587658</v>
@@ -7978,16 +7978,16 @@
         <v>0</v>
       </c>
       <c r="M29" s="2">
-        <v>268622</v>
+        <v>268638</v>
       </c>
       <c r="N29">
-        <v>34451</v>
+        <v>34453</v>
       </c>
       <c r="O29">
-        <v>0.1282508506376991</v>
+        <v>0.1282506570179945</v>
       </c>
       <c r="P29">
-        <v>0.4824751816155828</v>
+        <v>0.4824472549416838</v>
       </c>
       <c r="Q29">
         <v>35560</v>
@@ -8200,13 +8200,13 @@
         <v>0</v>
       </c>
       <c r="M32" s="2">
-        <v>249478</v>
+        <v>249481</v>
       </c>
       <c r="N32">
         <v>50676</v>
       </c>
       <c r="O32">
-        <v>0.2031281315386527</v>
+        <v>0.2031256889302191</v>
       </c>
       <c r="P32">
         <v>0.3487868284228769</v>
@@ -8274,16 +8274,16 @@
         <v>0</v>
       </c>
       <c r="M33" s="2">
-        <v>244605</v>
+        <v>244613</v>
       </c>
       <c r="N33">
-        <v>46844</v>
+        <v>46845</v>
       </c>
       <c r="O33">
-        <v>0.1915087590196439</v>
+        <v>0.1915065838692138</v>
       </c>
       <c r="P33">
-        <v>0.2639314928425358</v>
+        <v>0.263925870699755</v>
       </c>
       <c r="Q33">
         <v>90115</v>
@@ -8345,13 +8345,13 @@
         <v>0</v>
       </c>
       <c r="M34" s="2">
-        <v>112431</v>
+        <v>112433</v>
       </c>
       <c r="N34">
         <v>22805</v>
       </c>
       <c r="O34">
-        <v>0.2028355168948066</v>
+        <v>0.2028319087812297</v>
       </c>
       <c r="P34">
         <v>0.289456450556647</v>
@@ -8419,16 +8419,16 @@
         <v>0</v>
       </c>
       <c r="M35" s="2">
-        <v>152367</v>
+        <v>152371</v>
       </c>
       <c r="N35">
-        <v>96355</v>
+        <v>96359</v>
       </c>
       <c r="O35">
-        <v>0.6323875904887541</v>
+        <v>0.6323972409447992</v>
       </c>
       <c r="P35">
-        <v>0.1633922554559121</v>
+        <v>0.163385479841176</v>
       </c>
       <c r="Q35">
         <v>101188</v>
@@ -8493,16 +8493,16 @@
         <v>0</v>
       </c>
       <c r="M36" s="2">
-        <v>450791</v>
+        <v>450792</v>
       </c>
       <c r="N36">
-        <v>153418</v>
+        <v>153416</v>
       </c>
       <c r="O36">
-        <v>0.3403306632119985</v>
+        <v>0.3403254716144031</v>
       </c>
       <c r="P36">
-        <v>0.1050039734754231</v>
+        <v>0.1050053414627791</v>
       </c>
       <c r="Q36">
         <v>68668</v>
@@ -8567,16 +8567,16 @@
         <v>0</v>
       </c>
       <c r="M37" s="2">
-        <v>34094</v>
+        <v>34095</v>
       </c>
       <c r="N37">
-        <v>20350</v>
+        <v>20351</v>
       </c>
       <c r="O37">
-        <v>0.5968792162843902</v>
+        <v>0.5968910397418976</v>
       </c>
       <c r="P37">
-        <v>0.06503667481662592</v>
+        <v>0.06503349469463596</v>
       </c>
       <c r="Q37">
         <v>81333</v>
@@ -8641,16 +8641,16 @@
         <v>0</v>
       </c>
       <c r="M38" s="2">
-        <v>159716</v>
+        <v>159719</v>
       </c>
       <c r="N38">
-        <v>101282</v>
+        <v>101285</v>
       </c>
       <c r="O38">
-        <v>0.6341380951188359</v>
+        <v>0.6341449670984667</v>
       </c>
       <c r="P38">
-        <v>0.02051646248841017</v>
+        <v>0.02051585540267298</v>
       </c>
       <c r="Q38">
         <v>87622</v>

--- a/dashboard_data/latest_sourcing_rank.xlsx
+++ b/dashboard_data/latest_sourcing_rank.xlsx
@@ -63,7 +63,7 @@
     <t>주의</t>
   </si>
   <si>
-    <t>2026-06-21 16:11:00</t>
+    <t>2026-06-21 16:33:46</t>
   </si>
   <si>
     <t>점수는 소싱 후보 선별용입니다. 식품/화장품/KC/상표권/정품 증빙은 등록 전 별도 확인하세요.</t>
@@ -441,7 +441,7 @@
     <t>(국내매장판) 나이키 에어 포스 1 07 로우 올백 맨즈 | (국내매장판) 나이키 우먼스 에어 포스 1 07 에어포스 화이트 DD8959-100 A/S가능 | [국내매장판] 나이키 에어포스 1 07 로우 올백 올검 화이트 블랙 된장 브라운 여성 남성</t>
   </si>
   <si>
-    <t>[유니클로] 선글라스 스퀘어 | Black | 유니클로 선글라스 나로 블랙 481648 | 유니클로 스포츠 선글라스 하프림 484937</t>
+    <t>[유니클로] 선글라스 스퀘어 | Brown | 유니클로 선글라스 나로 블랙 481648 | 유니클로 스포츠 선글라스 하프림 484937</t>
   </si>
   <si>
     <t>나이키 스포츠 양말 러닝 발목 단목 중목 장목 운동 테니스 헬스 두꺼운 쿠션 | 나이키 양말 스우시 에브리데이 쿠션 장목 중목 단목 크루 삭스 | 정식매장판 나이키 에브리데이 쿠션 크루 삭스 양말 3켤레 세트 SX7664-100</t>
@@ -1269,13 +1269,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="2">
-        <v>28168</v>
+        <v>28172</v>
       </c>
       <c r="N2">
         <v>4250</v>
       </c>
       <c r="O2">
-        <v>0.1508804316955411</v>
+        <v>0.1508590089450518</v>
       </c>
       <c r="P2">
         <v>7.972413793103448</v>
@@ -1343,16 +1343,16 @@
         <v>0</v>
       </c>
       <c r="M3" s="2">
-        <v>154860</v>
+        <v>154866</v>
       </c>
       <c r="N3">
-        <v>23414</v>
+        <v>23415</v>
       </c>
       <c r="O3">
-        <v>0.1511946274053984</v>
+        <v>0.1511952268412692</v>
       </c>
       <c r="P3">
-        <v>3.900654928978481</v>
+        <v>3.900489049542845</v>
       </c>
       <c r="Q3">
         <v>50747</v>
@@ -1417,16 +1417,16 @@
         <v>0</v>
       </c>
       <c r="M4" s="2">
-        <v>5836</v>
+        <v>5837</v>
       </c>
       <c r="N4">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="O4">
-        <v>0.6513022618231665</v>
+        <v>0.6513620010279253</v>
       </c>
       <c r="P4">
-        <v>6.570110228146629</v>
+        <v>6.568426447975397</v>
       </c>
       <c r="Q4">
         <v>82306</v>
@@ -1491,16 +1491,16 @@
         <v>0</v>
       </c>
       <c r="M5" s="2">
-        <v>43956</v>
+        <v>43973</v>
       </c>
       <c r="N5">
-        <v>12690</v>
+        <v>12691</v>
       </c>
       <c r="O5">
-        <v>0.2886977886977887</v>
+        <v>0.2886089191094535</v>
       </c>
       <c r="P5">
-        <v>5.839718530101642</v>
+        <v>5.839261981080448</v>
       </c>
       <c r="Q5">
         <v>89641</v>
@@ -1565,16 +1565,16 @@
         <v>0</v>
       </c>
       <c r="M6" s="2">
-        <v>21231</v>
+        <v>21232</v>
       </c>
       <c r="N6">
-        <v>9982</v>
+        <v>9983</v>
       </c>
       <c r="O6">
-        <v>0.4701615562149687</v>
+        <v>0.4701865109269028</v>
       </c>
       <c r="P6">
-        <v>5.185479071612775</v>
+        <v>5.184964792224537</v>
       </c>
       <c r="Q6">
         <v>172899</v>
@@ -1639,16 +1639,16 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>29650</v>
+        <v>29655</v>
       </c>
       <c r="N7">
-        <v>10933</v>
+        <v>10932</v>
       </c>
       <c r="O7">
-        <v>0.3687352445193929</v>
+        <v>0.3686393525543753</v>
       </c>
       <c r="P7">
-        <v>4.501042327562766</v>
+        <v>4.501450326323423</v>
       </c>
       <c r="Q7">
         <v>102141</v>
@@ -1713,16 +1713,16 @@
         <v>0</v>
       </c>
       <c r="M8" s="2">
-        <v>94337</v>
+        <v>94334</v>
       </c>
       <c r="N8">
-        <v>20945</v>
+        <v>20943</v>
       </c>
       <c r="O8">
-        <v>0.2220231722441884</v>
+        <v>0.2220090317382916</v>
       </c>
       <c r="P8">
-        <v>3.524827750059397</v>
+        <v>3.525162761963598</v>
       </c>
       <c r="Q8">
         <v>53453</v>
@@ -1787,13 +1787,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="2">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="N9">
         <v>2524</v>
       </c>
       <c r="O9">
-        <v>0.6490100282849062</v>
+        <v>0.6491769547325102</v>
       </c>
       <c r="P9">
         <v>4.729420731707317</v>
@@ -1932,16 +1932,16 @@
         <v>0</v>
       </c>
       <c r="M11" s="2">
-        <v>72889</v>
+        <v>72887</v>
       </c>
       <c r="N11">
-        <v>45261</v>
+        <v>45260</v>
       </c>
       <c r="O11">
-        <v>0.6209578948812579</v>
+        <v>0.6209612139338977</v>
       </c>
       <c r="P11">
-        <v>0.8666034699411389</v>
+        <v>0.8666225749559083</v>
       </c>
       <c r="Q11">
         <v>106848</v>
@@ -2006,16 +2006,16 @@
         <v>0</v>
       </c>
       <c r="M12" s="2">
-        <v>44249</v>
+        <v>44248</v>
       </c>
       <c r="N12">
-        <v>23670</v>
+        <v>23671</v>
       </c>
       <c r="O12">
-        <v>0.534927342990802</v>
+        <v>0.5349620321822455</v>
       </c>
       <c r="P12">
-        <v>2.344131257888094</v>
+        <v>2.344032644819318</v>
       </c>
       <c r="Q12">
         <v>239490</v>
@@ -2080,16 +2080,16 @@
         <v>0</v>
       </c>
       <c r="M13" s="2">
-        <v>101734</v>
+        <v>101738</v>
       </c>
       <c r="N13">
-        <v>20523</v>
+        <v>20522</v>
       </c>
       <c r="O13">
-        <v>0.2017319676804215</v>
+        <v>0.2017142070809334</v>
       </c>
       <c r="P13">
-        <v>1.111380497502788</v>
+        <v>1.111434390456794</v>
       </c>
       <c r="Q13">
         <v>90115</v>
@@ -2151,13 +2151,13 @@
         <v>0</v>
       </c>
       <c r="M14" s="2">
-        <v>23855</v>
+        <v>23853</v>
       </c>
       <c r="N14">
         <v>10817</v>
       </c>
       <c r="O14">
-        <v>0.4534479144833368</v>
+        <v>0.4534859346832684</v>
       </c>
       <c r="P14">
         <v>2.261610332508931</v>
@@ -2302,13 +2302,13 @@
         <v>38697</v>
       </c>
       <c r="N16">
-        <v>4180</v>
+        <v>4182</v>
       </c>
       <c r="O16">
-        <v>0.1080187094606817</v>
+        <v>0.1080703930537251</v>
       </c>
       <c r="P16">
-        <v>2.186915887850467</v>
+        <v>2.185894441849603</v>
       </c>
       <c r="Q16">
         <v>75248</v>
@@ -2373,16 +2373,16 @@
         <v>0</v>
       </c>
       <c r="M17" s="2">
-        <v>379708</v>
+        <v>379723</v>
       </c>
       <c r="N17">
-        <v>52875</v>
+        <v>52874</v>
       </c>
       <c r="O17">
-        <v>0.1392517408113603</v>
+        <v>0.1392436065237028</v>
       </c>
       <c r="P17">
-        <v>0.7294006606890042</v>
+        <v>0.7294144297202401</v>
       </c>
       <c r="Q17">
         <v>46595</v>
@@ -2447,16 +2447,16 @@
         <v>0</v>
       </c>
       <c r="M18" s="2">
-        <v>637334</v>
+        <v>637758</v>
       </c>
       <c r="N18">
-        <v>271466</v>
+        <v>271468</v>
       </c>
       <c r="O18">
-        <v>0.4259399310251767</v>
+        <v>0.4256598898014607</v>
       </c>
       <c r="P18">
-        <v>0.4267839125663743</v>
+        <v>0.4267807694573735</v>
       </c>
       <c r="Q18">
         <v>122173</v>
@@ -2521,16 +2521,16 @@
         <v>0</v>
       </c>
       <c r="M19" s="2">
-        <v>149776</v>
+        <v>149780</v>
       </c>
       <c r="N19">
-        <v>68686</v>
+        <v>68691</v>
       </c>
       <c r="O19">
-        <v>0.4585914966349749</v>
+        <v>0.4586126318600614</v>
       </c>
       <c r="P19">
-        <v>0.7854796034076702</v>
+        <v>0.7854225116657703</v>
       </c>
       <c r="Q19">
         <v>101539</v>
@@ -2669,16 +2669,16 @@
         <v>0</v>
       </c>
       <c r="M21" s="2">
-        <v>89495</v>
+        <v>89493</v>
       </c>
       <c r="N21">
-        <v>11076</v>
+        <v>11075</v>
       </c>
       <c r="O21">
-        <v>0.123761103972289</v>
+        <v>0.1237526957415664</v>
       </c>
       <c r="P21">
-        <v>2.729957050823193</v>
+        <v>2.730201342281879</v>
       </c>
       <c r="Q21">
         <v>15396</v>
@@ -2743,16 +2743,16 @@
         <v>0</v>
       </c>
       <c r="M22" s="2">
-        <v>48250</v>
+        <v>48274</v>
       </c>
       <c r="N22">
-        <v>24505</v>
+        <v>24506</v>
       </c>
       <c r="O22">
-        <v>0.5078756476683938</v>
+        <v>0.5076438662634131</v>
       </c>
       <c r="P22">
-        <v>1.167242430400325</v>
+        <v>1.167194993091116</v>
       </c>
       <c r="Q22">
         <v>157273</v>
@@ -2817,16 +2817,16 @@
         <v>0</v>
       </c>
       <c r="M23" s="2">
-        <v>422659</v>
+        <v>422669</v>
       </c>
       <c r="N23">
-        <v>280397</v>
+        <v>280393</v>
       </c>
       <c r="O23">
-        <v>0.6634118757674626</v>
+        <v>0.6633867163193894</v>
       </c>
       <c r="P23">
-        <v>0.2917678263938652</v>
+        <v>0.2917719871797157</v>
       </c>
       <c r="Q23">
         <v>156599</v>
@@ -2891,16 +2891,16 @@
         <v>0</v>
       </c>
       <c r="M24" s="2">
-        <v>1908183</v>
+        <v>1908190</v>
       </c>
       <c r="N24">
-        <v>705901</v>
+        <v>705921</v>
       </c>
       <c r="O24">
-        <v>0.3699335965156382</v>
+        <v>0.3699427205886207</v>
       </c>
       <c r="P24">
-        <v>0.2215294312614288</v>
+        <v>0.2215231558268097</v>
       </c>
       <c r="Q24">
         <v>91990</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="M25" s="2">
-        <v>346537</v>
+        <v>346524</v>
       </c>
       <c r="N25">
-        <v>77854</v>
+        <v>77852</v>
       </c>
       <c r="O25">
-        <v>0.2246628787113641</v>
+        <v>0.2246655354318893</v>
       </c>
       <c r="P25">
-        <v>0.4779741899068681</v>
+        <v>0.4779864532019704</v>
       </c>
       <c r="Q25">
         <v>30810</v>
@@ -3039,16 +3039,16 @@
         <v>0</v>
       </c>
       <c r="M26" s="2">
-        <v>93989</v>
+        <v>93994</v>
       </c>
       <c r="N26">
-        <v>17045</v>
+        <v>17047</v>
       </c>
       <c r="O26">
-        <v>0.1813510091606464</v>
+        <v>0.1813626401685214</v>
       </c>
       <c r="P26">
-        <v>0.9192184310294547</v>
+        <v>0.9191112147897591</v>
       </c>
       <c r="Q26">
         <v>40699</v>
@@ -3113,16 +3113,16 @@
         <v>0</v>
       </c>
       <c r="M27" s="2">
-        <v>1376959</v>
+        <v>1377162</v>
       </c>
       <c r="N27">
-        <v>517411</v>
+        <v>517447</v>
       </c>
       <c r="O27">
-        <v>0.3757635485152426</v>
+        <v>0.375734299958901</v>
       </c>
       <c r="P27">
-        <v>0.1991648486698833</v>
+        <v>0.1991509949820982</v>
       </c>
       <c r="Q27">
         <v>50682</v>
@@ -3187,13 +3187,13 @@
         <v>0</v>
       </c>
       <c r="M28" s="2">
-        <v>138456</v>
+        <v>138462</v>
       </c>
       <c r="N28">
         <v>19476</v>
       </c>
       <c r="O28">
-        <v>0.140665626625065</v>
+        <v>0.1406595311348962</v>
       </c>
       <c r="P28">
         <v>0.3902738046587658</v>
@@ -3258,13 +3258,13 @@
         <v>0</v>
       </c>
       <c r="M29" s="2">
-        <v>268638</v>
+        <v>268653</v>
       </c>
       <c r="N29">
         <v>34453</v>
       </c>
       <c r="O29">
-        <v>0.1282506570179945</v>
+        <v>0.1282434962572538</v>
       </c>
       <c r="P29">
         <v>0.4824472549416838</v>
@@ -3332,16 +3332,16 @@
         <v>0</v>
       </c>
       <c r="M30" s="2">
-        <v>106909</v>
+        <v>106915</v>
       </c>
       <c r="N30">
-        <v>39031</v>
+        <v>39030</v>
       </c>
       <c r="O30">
-        <v>0.365086194801186</v>
+        <v>0.365056353177758</v>
       </c>
       <c r="P30">
-        <v>0.4605044593800312</v>
+        <v>0.4605162279580884</v>
       </c>
       <c r="Q30">
         <v>65377</v>
@@ -3683,13 +3683,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="2">
-        <v>28168</v>
+        <v>28172</v>
       </c>
       <c r="N2">
         <v>4250</v>
       </c>
       <c r="O2">
-        <v>0.1508804316955411</v>
+        <v>0.1508590089450518</v>
       </c>
       <c r="P2">
         <v>7.972413793103448</v>
@@ -3757,16 +3757,16 @@
         <v>0</v>
       </c>
       <c r="M3" s="2">
-        <v>154860</v>
+        <v>154866</v>
       </c>
       <c r="N3">
-        <v>23414</v>
+        <v>23415</v>
       </c>
       <c r="O3">
-        <v>0.1511946274053984</v>
+        <v>0.1511952268412692</v>
       </c>
       <c r="P3">
-        <v>3.900654928978481</v>
+        <v>3.900489049542845</v>
       </c>
       <c r="Q3">
         <v>50747</v>
@@ -3831,16 +3831,16 @@
         <v>0</v>
       </c>
       <c r="M4" s="2">
-        <v>5836</v>
+        <v>5837</v>
       </c>
       <c r="N4">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="O4">
-        <v>0.6513022618231665</v>
+        <v>0.6513620010279253</v>
       </c>
       <c r="P4">
-        <v>6.570110228146629</v>
+        <v>6.568426447975397</v>
       </c>
       <c r="Q4">
         <v>82306</v>
@@ -3905,16 +3905,16 @@
         <v>0</v>
       </c>
       <c r="M5" s="2">
-        <v>43956</v>
+        <v>43973</v>
       </c>
       <c r="N5">
-        <v>12690</v>
+        <v>12691</v>
       </c>
       <c r="O5">
-        <v>0.2886977886977887</v>
+        <v>0.2886089191094535</v>
       </c>
       <c r="P5">
-        <v>5.839718530101642</v>
+        <v>5.839261981080448</v>
       </c>
       <c r="Q5">
         <v>89641</v>
@@ -3979,16 +3979,16 @@
         <v>0</v>
       </c>
       <c r="M6" s="2">
-        <v>21231</v>
+        <v>21232</v>
       </c>
       <c r="N6">
-        <v>9982</v>
+        <v>9983</v>
       </c>
       <c r="O6">
-        <v>0.4701615562149687</v>
+        <v>0.4701865109269028</v>
       </c>
       <c r="P6">
-        <v>5.185479071612775</v>
+        <v>5.184964792224537</v>
       </c>
       <c r="Q6">
         <v>172899</v>
@@ -4053,16 +4053,16 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>29650</v>
+        <v>29655</v>
       </c>
       <c r="N7">
-        <v>10933</v>
+        <v>10932</v>
       </c>
       <c r="O7">
-        <v>0.3687352445193929</v>
+        <v>0.3686393525543753</v>
       </c>
       <c r="P7">
-        <v>4.501042327562766</v>
+        <v>4.501450326323423</v>
       </c>
       <c r="Q7">
         <v>102141</v>
@@ -4127,16 +4127,16 @@
         <v>0</v>
       </c>
       <c r="M8" s="2">
-        <v>94337</v>
+        <v>94334</v>
       </c>
       <c r="N8">
-        <v>20945</v>
+        <v>20943</v>
       </c>
       <c r="O8">
-        <v>0.2220231722441884</v>
+        <v>0.2220090317382916</v>
       </c>
       <c r="P8">
-        <v>3.524827750059397</v>
+        <v>3.525162761963598</v>
       </c>
       <c r="Q8">
         <v>53453</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="2">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="N9">
         <v>2524</v>
       </c>
       <c r="O9">
-        <v>0.6490100282849062</v>
+        <v>0.6491769547325102</v>
       </c>
       <c r="P9">
         <v>4.729420731707317</v>
@@ -4346,16 +4346,16 @@
         <v>0</v>
       </c>
       <c r="M11" s="2">
-        <v>72889</v>
+        <v>72887</v>
       </c>
       <c r="N11">
-        <v>45261</v>
+        <v>45260</v>
       </c>
       <c r="O11">
-        <v>0.6209578948812579</v>
+        <v>0.6209612139338977</v>
       </c>
       <c r="P11">
-        <v>0.8666034699411389</v>
+        <v>0.8666225749559083</v>
       </c>
       <c r="Q11">
         <v>106848</v>
@@ -4420,16 +4420,16 @@
         <v>0</v>
       </c>
       <c r="M12" s="2">
-        <v>44249</v>
+        <v>44248</v>
       </c>
       <c r="N12">
-        <v>23670</v>
+        <v>23671</v>
       </c>
       <c r="O12">
-        <v>0.534927342990802</v>
+        <v>0.5349620321822455</v>
       </c>
       <c r="P12">
-        <v>2.344131257888094</v>
+        <v>2.344032644819318</v>
       </c>
       <c r="Q12">
         <v>239490</v>
@@ -4494,16 +4494,16 @@
         <v>0</v>
       </c>
       <c r="M13" s="2">
-        <v>101734</v>
+        <v>101738</v>
       </c>
       <c r="N13">
-        <v>20523</v>
+        <v>20522</v>
       </c>
       <c r="O13">
-        <v>0.2017319676804215</v>
+        <v>0.2017142070809334</v>
       </c>
       <c r="P13">
-        <v>1.111380497502788</v>
+        <v>1.111434390456794</v>
       </c>
       <c r="Q13">
         <v>90115</v>
@@ -4565,13 +4565,13 @@
         <v>0</v>
       </c>
       <c r="M14" s="2">
-        <v>23855</v>
+        <v>23853</v>
       </c>
       <c r="N14">
         <v>10817</v>
       </c>
       <c r="O14">
-        <v>0.4534479144833368</v>
+        <v>0.4534859346832684</v>
       </c>
       <c r="P14">
         <v>2.261610332508931</v>
@@ -4716,13 +4716,13 @@
         <v>38697</v>
       </c>
       <c r="N16">
-        <v>4180</v>
+        <v>4182</v>
       </c>
       <c r="O16">
-        <v>0.1080187094606817</v>
+        <v>0.1080703930537251</v>
       </c>
       <c r="P16">
-        <v>2.186915887850467</v>
+        <v>2.185894441849603</v>
       </c>
       <c r="Q16">
         <v>75248</v>
@@ -4787,16 +4787,16 @@
         <v>0</v>
       </c>
       <c r="M17" s="2">
-        <v>379708</v>
+        <v>379723</v>
       </c>
       <c r="N17">
-        <v>52875</v>
+        <v>52874</v>
       </c>
       <c r="O17">
-        <v>0.1392517408113603</v>
+        <v>0.1392436065237028</v>
       </c>
       <c r="P17">
-        <v>0.7294006606890042</v>
+        <v>0.7294144297202401</v>
       </c>
       <c r="Q17">
         <v>46595</v>
@@ -4861,16 +4861,16 @@
         <v>0</v>
       </c>
       <c r="M18" s="2">
-        <v>637334</v>
+        <v>637758</v>
       </c>
       <c r="N18">
-        <v>271466</v>
+        <v>271468</v>
       </c>
       <c r="O18">
-        <v>0.4259399310251767</v>
+        <v>0.4256598898014607</v>
       </c>
       <c r="P18">
-        <v>0.4267839125663743</v>
+        <v>0.4267807694573735</v>
       </c>
       <c r="Q18">
         <v>122173</v>
@@ -4935,16 +4935,16 @@
         <v>0</v>
       </c>
       <c r="M19" s="2">
-        <v>149776</v>
+        <v>149780</v>
       </c>
       <c r="N19">
-        <v>68686</v>
+        <v>68691</v>
       </c>
       <c r="O19">
-        <v>0.4585914966349749</v>
+        <v>0.4586126318600614</v>
       </c>
       <c r="P19">
-        <v>0.7854796034076702</v>
+        <v>0.7854225116657703</v>
       </c>
       <c r="Q19">
         <v>101539</v>
@@ -5083,16 +5083,16 @@
         <v>0</v>
       </c>
       <c r="M21" s="2">
-        <v>89495</v>
+        <v>89493</v>
       </c>
       <c r="N21">
-        <v>11076</v>
+        <v>11075</v>
       </c>
       <c r="O21">
-        <v>0.123761103972289</v>
+        <v>0.1237526957415664</v>
       </c>
       <c r="P21">
-        <v>2.729957050823193</v>
+        <v>2.730201342281879</v>
       </c>
       <c r="Q21">
         <v>15396</v>
@@ -5157,16 +5157,16 @@
         <v>0</v>
       </c>
       <c r="M22" s="2">
-        <v>48250</v>
+        <v>48274</v>
       </c>
       <c r="N22">
-        <v>24505</v>
+        <v>24506</v>
       </c>
       <c r="O22">
-        <v>0.5078756476683938</v>
+        <v>0.5076438662634131</v>
       </c>
       <c r="P22">
-        <v>1.167242430400325</v>
+        <v>1.167194993091116</v>
       </c>
       <c r="Q22">
         <v>157273</v>
@@ -5231,16 +5231,16 @@
         <v>0</v>
       </c>
       <c r="M23" s="2">
-        <v>422659</v>
+        <v>422669</v>
       </c>
       <c r="N23">
-        <v>280397</v>
+        <v>280393</v>
       </c>
       <c r="O23">
-        <v>0.6634118757674626</v>
+        <v>0.6633867163193894</v>
       </c>
       <c r="P23">
-        <v>0.2917678263938652</v>
+        <v>0.2917719871797157</v>
       </c>
       <c r="Q23">
         <v>156599</v>
@@ -5305,16 +5305,16 @@
         <v>0</v>
       </c>
       <c r="M24" s="2">
-        <v>1908183</v>
+        <v>1908190</v>
       </c>
       <c r="N24">
-        <v>705901</v>
+        <v>705921</v>
       </c>
       <c r="O24">
-        <v>0.3699335965156382</v>
+        <v>0.3699427205886207</v>
       </c>
       <c r="P24">
-        <v>0.2215294312614288</v>
+        <v>0.2215231558268097</v>
       </c>
       <c r="Q24">
         <v>91990</v>
@@ -5379,16 +5379,16 @@
         <v>0</v>
       </c>
       <c r="M25" s="2">
-        <v>346537</v>
+        <v>346524</v>
       </c>
       <c r="N25">
-        <v>77854</v>
+        <v>77852</v>
       </c>
       <c r="O25">
-        <v>0.2246628787113641</v>
+        <v>0.2246655354318893</v>
       </c>
       <c r="P25">
-        <v>0.4779741899068681</v>
+        <v>0.4779864532019704</v>
       </c>
       <c r="Q25">
         <v>30810</v>
@@ -5453,16 +5453,16 @@
         <v>0</v>
       </c>
       <c r="M26" s="2">
-        <v>93989</v>
+        <v>93994</v>
       </c>
       <c r="N26">
-        <v>17045</v>
+        <v>17047</v>
       </c>
       <c r="O26">
-        <v>0.1813510091606464</v>
+        <v>0.1813626401685214</v>
       </c>
       <c r="P26">
-        <v>0.9192184310294547</v>
+        <v>0.9191112147897591</v>
       </c>
       <c r="Q26">
         <v>40699</v>
@@ -5527,16 +5527,16 @@
         <v>0</v>
       </c>
       <c r="M27" s="2">
-        <v>1376959</v>
+        <v>1377162</v>
       </c>
       <c r="N27">
-        <v>517411</v>
+        <v>517447</v>
       </c>
       <c r="O27">
-        <v>0.3757635485152426</v>
+        <v>0.375734299958901</v>
       </c>
       <c r="P27">
-        <v>0.1991648486698833</v>
+        <v>0.1991509949820982</v>
       </c>
       <c r="Q27">
         <v>50682</v>
@@ -5601,13 +5601,13 @@
         <v>0</v>
       </c>
       <c r="M28" s="2">
-        <v>138456</v>
+        <v>138462</v>
       </c>
       <c r="N28">
         <v>19476</v>
       </c>
       <c r="O28">
-        <v>0.140665626625065</v>
+        <v>0.1406595311348962</v>
       </c>
       <c r="P28">
         <v>0.3902738046587658</v>
@@ -5672,13 +5672,13 @@
         <v>0</v>
       </c>
       <c r="M29" s="2">
-        <v>268638</v>
+        <v>268653</v>
       </c>
       <c r="N29">
         <v>34453</v>
       </c>
       <c r="O29">
-        <v>0.1282506570179945</v>
+        <v>0.1282434962572538</v>
       </c>
       <c r="P29">
         <v>0.4824472549416838</v>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="M30" s="2">
-        <v>106909</v>
+        <v>106915</v>
       </c>
       <c r="N30">
-        <v>39031</v>
+        <v>39030</v>
       </c>
       <c r="O30">
-        <v>0.365086194801186</v>
+        <v>0.365056353177758</v>
       </c>
       <c r="P30">
-        <v>0.4605044593800312</v>
+        <v>0.4605162279580884</v>
       </c>
       <c r="Q30">
         <v>65377</v>
@@ -5989,13 +5989,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="2">
-        <v>28168</v>
+        <v>28172</v>
       </c>
       <c r="N2">
         <v>4250</v>
       </c>
       <c r="O2">
-        <v>0.1508804316955411</v>
+        <v>0.1508590089450518</v>
       </c>
       <c r="P2">
         <v>7.972413793103448</v>
@@ -6063,16 +6063,16 @@
         <v>0</v>
       </c>
       <c r="M3" s="2">
-        <v>154860</v>
+        <v>154866</v>
       </c>
       <c r="N3">
-        <v>23414</v>
+        <v>23415</v>
       </c>
       <c r="O3">
-        <v>0.1511946274053984</v>
+        <v>0.1511952268412692</v>
       </c>
       <c r="P3">
-        <v>3.900654928978481</v>
+        <v>3.900489049542845</v>
       </c>
       <c r="Q3">
         <v>50747</v>
@@ -6137,16 +6137,16 @@
         <v>0</v>
       </c>
       <c r="M4" s="2">
-        <v>5836</v>
+        <v>5837</v>
       </c>
       <c r="N4">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="O4">
-        <v>0.6513022618231665</v>
+        <v>0.6513620010279253</v>
       </c>
       <c r="P4">
-        <v>6.570110228146629</v>
+        <v>6.568426447975397</v>
       </c>
       <c r="Q4">
         <v>82306</v>
@@ -6211,16 +6211,16 @@
         <v>0</v>
       </c>
       <c r="M5" s="2">
-        <v>43956</v>
+        <v>43973</v>
       </c>
       <c r="N5">
-        <v>12690</v>
+        <v>12691</v>
       </c>
       <c r="O5">
-        <v>0.2886977886977887</v>
+        <v>0.2886089191094535</v>
       </c>
       <c r="P5">
-        <v>5.839718530101642</v>
+        <v>5.839261981080448</v>
       </c>
       <c r="Q5">
         <v>89641</v>
@@ -6285,16 +6285,16 @@
         <v>0</v>
       </c>
       <c r="M6" s="2">
-        <v>21231</v>
+        <v>21232</v>
       </c>
       <c r="N6">
-        <v>9982</v>
+        <v>9983</v>
       </c>
       <c r="O6">
-        <v>0.4701615562149687</v>
+        <v>0.4701865109269028</v>
       </c>
       <c r="P6">
-        <v>5.185479071612775</v>
+        <v>5.184964792224537</v>
       </c>
       <c r="Q6">
         <v>172899</v>
@@ -6359,16 +6359,16 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>29650</v>
+        <v>29655</v>
       </c>
       <c r="N7">
-        <v>10933</v>
+        <v>10932</v>
       </c>
       <c r="O7">
-        <v>0.3687352445193929</v>
+        <v>0.3686393525543753</v>
       </c>
       <c r="P7">
-        <v>4.501042327562766</v>
+        <v>4.501450326323423</v>
       </c>
       <c r="Q7">
         <v>102141</v>
@@ -6433,16 +6433,16 @@
         <v>0</v>
       </c>
       <c r="M8" s="2">
-        <v>94337</v>
+        <v>94334</v>
       </c>
       <c r="N8">
-        <v>20945</v>
+        <v>20943</v>
       </c>
       <c r="O8">
-        <v>0.2220231722441884</v>
+        <v>0.2220090317382916</v>
       </c>
       <c r="P8">
-        <v>3.524827750059397</v>
+        <v>3.525162761963598</v>
       </c>
       <c r="Q8">
         <v>53453</v>
@@ -6507,13 +6507,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="2">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="N9">
         <v>2524</v>
       </c>
       <c r="O9">
-        <v>0.6490100282849062</v>
+        <v>0.6491769547325102</v>
       </c>
       <c r="P9">
         <v>4.729420731707317</v>
@@ -6652,16 +6652,16 @@
         <v>0</v>
       </c>
       <c r="M11" s="2">
-        <v>72889</v>
+        <v>72887</v>
       </c>
       <c r="N11">
-        <v>45261</v>
+        <v>45260</v>
       </c>
       <c r="O11">
-        <v>0.6209578948812579</v>
+        <v>0.6209612139338977</v>
       </c>
       <c r="P11">
-        <v>0.8666034699411389</v>
+        <v>0.8666225749559083</v>
       </c>
       <c r="Q11">
         <v>106848</v>
@@ -6726,16 +6726,16 @@
         <v>0</v>
       </c>
       <c r="M12" s="2">
-        <v>44249</v>
+        <v>44248</v>
       </c>
       <c r="N12">
-        <v>23670</v>
+        <v>23671</v>
       </c>
       <c r="O12">
-        <v>0.534927342990802</v>
+        <v>0.5349620321822455</v>
       </c>
       <c r="P12">
-        <v>2.344131257888094</v>
+        <v>2.344032644819318</v>
       </c>
       <c r="Q12">
         <v>239490</v>
@@ -6800,16 +6800,16 @@
         <v>0</v>
       </c>
       <c r="M13" s="2">
-        <v>101734</v>
+        <v>101738</v>
       </c>
       <c r="N13">
-        <v>20523</v>
+        <v>20522</v>
       </c>
       <c r="O13">
-        <v>0.2017319676804215</v>
+        <v>0.2017142070809334</v>
       </c>
       <c r="P13">
-        <v>1.111380497502788</v>
+        <v>1.111434390456794</v>
       </c>
       <c r="Q13">
         <v>90115</v>
@@ -6871,13 +6871,13 @@
         <v>0</v>
       </c>
       <c r="M14" s="2">
-        <v>23855</v>
+        <v>23853</v>
       </c>
       <c r="N14">
         <v>10817</v>
       </c>
       <c r="O14">
-        <v>0.4534479144833368</v>
+        <v>0.4534859346832684</v>
       </c>
       <c r="P14">
         <v>2.261610332508931</v>
@@ -7022,13 +7022,13 @@
         <v>38697</v>
       </c>
       <c r="N16">
-        <v>4180</v>
+        <v>4182</v>
       </c>
       <c r="O16">
-        <v>0.1080187094606817</v>
+        <v>0.1080703930537251</v>
       </c>
       <c r="P16">
-        <v>2.186915887850467</v>
+        <v>2.185894441849603</v>
       </c>
       <c r="Q16">
         <v>75248</v>
@@ -7093,16 +7093,16 @@
         <v>0</v>
       </c>
       <c r="M17" s="2">
-        <v>379708</v>
+        <v>379723</v>
       </c>
       <c r="N17">
-        <v>52875</v>
+        <v>52874</v>
       </c>
       <c r="O17">
-        <v>0.1392517408113603</v>
+        <v>0.1392436065237028</v>
       </c>
       <c r="P17">
-        <v>0.7294006606890042</v>
+        <v>0.7294144297202401</v>
       </c>
       <c r="Q17">
         <v>46595</v>
@@ -7167,16 +7167,16 @@
         <v>0</v>
       </c>
       <c r="M18" s="2">
-        <v>637334</v>
+        <v>637758</v>
       </c>
       <c r="N18">
-        <v>271466</v>
+        <v>271468</v>
       </c>
       <c r="O18">
-        <v>0.4259399310251767</v>
+        <v>0.4256598898014607</v>
       </c>
       <c r="P18">
-        <v>0.4267839125663743</v>
+        <v>0.4267807694573735</v>
       </c>
       <c r="Q18">
         <v>122173</v>
@@ -7241,16 +7241,16 @@
         <v>0</v>
       </c>
       <c r="M19" s="2">
-        <v>149776</v>
+        <v>149780</v>
       </c>
       <c r="N19">
-        <v>68686</v>
+        <v>68691</v>
       </c>
       <c r="O19">
-        <v>0.4585914966349749</v>
+        <v>0.4586126318600614</v>
       </c>
       <c r="P19">
-        <v>0.7854796034076702</v>
+        <v>0.7854225116657703</v>
       </c>
       <c r="Q19">
         <v>101539</v>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="M21" s="2">
-        <v>89495</v>
+        <v>89493</v>
       </c>
       <c r="N21">
-        <v>11076</v>
+        <v>11075</v>
       </c>
       <c r="O21">
-        <v>0.123761103972289</v>
+        <v>0.1237526957415664</v>
       </c>
       <c r="P21">
-        <v>2.729957050823193</v>
+        <v>2.730201342281879</v>
       </c>
       <c r="Q21">
         <v>15396</v>
@@ -7463,16 +7463,16 @@
         <v>0</v>
       </c>
       <c r="M22" s="2">
-        <v>48250</v>
+        <v>48274</v>
       </c>
       <c r="N22">
-        <v>24505</v>
+        <v>24506</v>
       </c>
       <c r="O22">
-        <v>0.5078756476683938</v>
+        <v>0.5076438662634131</v>
       </c>
       <c r="P22">
-        <v>1.167242430400325</v>
+        <v>1.167194993091116</v>
       </c>
       <c r="Q22">
         <v>157273</v>
@@ -7537,16 +7537,16 @@
         <v>0</v>
       </c>
       <c r="M23" s="2">
-        <v>422659</v>
+        <v>422669</v>
       </c>
       <c r="N23">
-        <v>280397</v>
+        <v>280393</v>
       </c>
       <c r="O23">
-        <v>0.6634118757674626</v>
+        <v>0.6633867163193894</v>
       </c>
       <c r="P23">
-        <v>0.2917678263938652</v>
+        <v>0.2917719871797157</v>
       </c>
       <c r="Q23">
         <v>156599</v>
@@ -7611,16 +7611,16 @@
         <v>0</v>
       </c>
       <c r="M24" s="2">
-        <v>1908183</v>
+        <v>1908190</v>
       </c>
       <c r="N24">
-        <v>705901</v>
+        <v>705921</v>
       </c>
       <c r="O24">
-        <v>0.3699335965156382</v>
+        <v>0.3699427205886207</v>
       </c>
       <c r="P24">
-        <v>0.2215294312614288</v>
+        <v>0.2215231558268097</v>
       </c>
       <c r="Q24">
         <v>91990</v>
@@ -7685,16 +7685,16 @@
         <v>0</v>
       </c>
       <c r="M25" s="2">
-        <v>346537</v>
+        <v>346524</v>
       </c>
       <c r="N25">
-        <v>77854</v>
+        <v>77852</v>
       </c>
       <c r="O25">
-        <v>0.2246628787113641</v>
+        <v>0.2246655354318893</v>
       </c>
       <c r="P25">
-        <v>0.4779741899068681</v>
+        <v>0.4779864532019704</v>
       </c>
       <c r="Q25">
         <v>30810</v>
@@ -7759,16 +7759,16 @@
         <v>0</v>
       </c>
       <c r="M26" s="2">
-        <v>93989</v>
+        <v>93994</v>
       </c>
       <c r="N26">
-        <v>17045</v>
+        <v>17047</v>
       </c>
       <c r="O26">
-        <v>0.1813510091606464</v>
+        <v>0.1813626401685214</v>
       </c>
       <c r="P26">
-        <v>0.9192184310294547</v>
+        <v>0.9191112147897591</v>
       </c>
       <c r="Q26">
         <v>40699</v>
@@ -7833,16 +7833,16 @@
         <v>0</v>
       </c>
       <c r="M27" s="2">
-        <v>1376959</v>
+        <v>1377162</v>
       </c>
       <c r="N27">
-        <v>517411</v>
+        <v>517447</v>
       </c>
       <c r="O27">
-        <v>0.3757635485152426</v>
+        <v>0.375734299958901</v>
       </c>
       <c r="P27">
-        <v>0.1991648486698833</v>
+        <v>0.1991509949820982</v>
       </c>
       <c r="Q27">
         <v>50682</v>
@@ -7907,13 +7907,13 @@
         <v>0</v>
       </c>
       <c r="M28" s="2">
-        <v>138456</v>
+        <v>138462</v>
       </c>
       <c r="N28">
         <v>19476</v>
       </c>
       <c r="O28">
-        <v>0.140665626625065</v>
+        <v>0.1406595311348962</v>
       </c>
       <c r="P28">
         <v>0.3902738046587658</v>
@@ -7978,13 +7978,13 @@
         <v>0</v>
       </c>
       <c r="M29" s="2">
-        <v>268638</v>
+        <v>268653</v>
       </c>
       <c r="N29">
         <v>34453</v>
       </c>
       <c r="O29">
-        <v>0.1282506570179945</v>
+        <v>0.1282434962572538</v>
       </c>
       <c r="P29">
         <v>0.4824472549416838</v>
@@ -8052,16 +8052,16 @@
         <v>0</v>
       </c>
       <c r="M30" s="2">
-        <v>106909</v>
+        <v>106915</v>
       </c>
       <c r="N30">
-        <v>39031</v>
+        <v>39030</v>
       </c>
       <c r="O30">
-        <v>0.365086194801186</v>
+        <v>0.365056353177758</v>
       </c>
       <c r="P30">
-        <v>0.4605044593800312</v>
+        <v>0.4605162279580884</v>
       </c>
       <c r="Q30">
         <v>65377</v>
@@ -8200,16 +8200,16 @@
         <v>0</v>
       </c>
       <c r="M32" s="2">
-        <v>249481</v>
+        <v>249482</v>
       </c>
       <c r="N32">
-        <v>50676</v>
+        <v>50678</v>
       </c>
       <c r="O32">
-        <v>0.2031256889302191</v>
+        <v>0.203132891350879</v>
       </c>
       <c r="P32">
-        <v>0.3487868284228769</v>
+        <v>0.3487730907085746</v>
       </c>
       <c r="Q32">
         <v>33975</v>
@@ -8274,16 +8274,16 @@
         <v>0</v>
       </c>
       <c r="M33" s="2">
-        <v>244613</v>
+        <v>244626</v>
       </c>
       <c r="N33">
-        <v>46845</v>
+        <v>46842</v>
       </c>
       <c r="O33">
-        <v>0.1915065838692138</v>
+        <v>0.191484143140958</v>
       </c>
       <c r="P33">
-        <v>0.263925870699755</v>
+        <v>0.2639427378467045</v>
       </c>
       <c r="Q33">
         <v>90115</v>
@@ -8345,16 +8345,16 @@
         <v>0</v>
       </c>
       <c r="M34" s="2">
-        <v>112433</v>
+        <v>112440</v>
       </c>
       <c r="N34">
-        <v>22805</v>
+        <v>22803</v>
       </c>
       <c r="O34">
-        <v>0.2028319087812297</v>
+        <v>0.2028014941302028</v>
       </c>
       <c r="P34">
-        <v>0.289456450556647</v>
+        <v>0.2894817272846352</v>
       </c>
       <c r="Q34">
         <v>42095</v>
@@ -8419,16 +8419,16 @@
         <v>0</v>
       </c>
       <c r="M35" s="2">
-        <v>152371</v>
+        <v>152377</v>
       </c>
       <c r="N35">
-        <v>96359</v>
+        <v>96361</v>
       </c>
       <c r="O35">
-        <v>0.6323972409447992</v>
+        <v>0.6323854649979984</v>
       </c>
       <c r="P35">
-        <v>0.163385479841176</v>
+        <v>0.1633820922445341</v>
       </c>
       <c r="Q35">
         <v>101188</v>
@@ -8493,16 +8493,16 @@
         <v>0</v>
       </c>
       <c r="M36" s="2">
-        <v>450792</v>
+        <v>450829</v>
       </c>
       <c r="N36">
-        <v>153416</v>
+        <v>153445</v>
       </c>
       <c r="O36">
-        <v>0.3403254716144031</v>
+        <v>0.3403618666944673</v>
       </c>
       <c r="P36">
-        <v>0.1050053414627791</v>
+        <v>0.1049855091341301</v>
       </c>
       <c r="Q36">
         <v>68668</v>
@@ -8567,16 +8567,16 @@
         <v>0</v>
       </c>
       <c r="M37" s="2">
-        <v>34095</v>
+        <v>34102</v>
       </c>
       <c r="N37">
-        <v>20351</v>
+        <v>20355</v>
       </c>
       <c r="O37">
-        <v>0.5968910397418976</v>
+        <v>0.596885813148789</v>
       </c>
       <c r="P37">
-        <v>0.06503349469463596</v>
+        <v>0.06502077731605964</v>
       </c>
       <c r="Q37">
         <v>81333</v>
@@ -8641,16 +8641,16 @@
         <v>0</v>
       </c>
       <c r="M38" s="2">
-        <v>159719</v>
+        <v>159724</v>
       </c>
       <c r="N38">
-        <v>101285</v>
+        <v>101289</v>
       </c>
       <c r="O38">
-        <v>0.6341449670984667</v>
+        <v>0.6341501590243169</v>
       </c>
       <c r="P38">
-        <v>0.02051585540267298</v>
+        <v>0.02051504601090848</v>
       </c>
       <c r="Q38">
         <v>87622</v>
